--- a/backend/order/src/test/resources/workbooks/DS-ORDER-3X/confirmed/CONFIRMED_ORDER_JAN.xlsx
+++ b/backend/order/src/test/resources/workbooks/DS-ORDER-3X/confirmed/CONFIRMED_ORDER_JAN.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C201"/>
+  <dimension ref="A1:C160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,11 +436,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>354</v>
+        <v>14</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -451,11 +451,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>340</v>
+        <v>229</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -466,11 +466,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>171</v>
+        <v>295</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>981</v>
+        <v>838</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -496,11 +496,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>820</v>
+        <v>601</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -511,11 +511,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>28415-08400</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>993</v>
+        <v>828</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -526,11 +526,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>674</v>
+        <v>201</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>188</v>
+        <v>343</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -556,11 +556,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>585</v>
+        <v>478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -571,11 +571,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>920</v>
+        <v>278</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -586,11 +586,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>815</v>
+        <v>893</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -601,11 +601,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>238</v>
+        <v>550</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>613</v>
+        <v>330</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -631,11 +631,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -646,11 +646,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>761</v>
+        <v>411</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -661,11 +661,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>311</v>
+        <v>126</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -676,11 +676,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>191</v>
+        <v>370</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -691,11 +691,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>642</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -706,11 +706,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>981</v>
+        <v>843</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -721,11 +721,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>410</v>
+        <v>732</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -736,11 +736,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>43</v>
+        <v>950</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -751,11 +751,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>626</v>
+        <v>614</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -766,11 +766,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>953</v>
+        <v>698</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -781,11 +781,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>236</v>
+        <v>330</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -796,11 +796,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>28415-08400</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>589</v>
+        <v>254</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -811,11 +811,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>969</v>
+        <v>129</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -826,11 +826,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>154</v>
+        <v>392</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -841,11 +841,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>773</v>
+        <v>154</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -856,11 +856,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>253</v>
+        <v>407</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -871,11 +871,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>337</v>
+        <v>620</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>661</v>
+        <v>598</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -901,11 +901,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>851</v>
+        <v>443</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -916,11 +916,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>696</v>
+        <v>508</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>756</v>
+        <v>560</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -946,11 +946,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>467</v>
+        <v>951</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -961,11 +961,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>281</v>
+        <v>963</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -976,11 +976,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>265</v>
+        <v>578</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -991,11 +991,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>79</v>
+        <v>511</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1006,11 +1006,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>272</v>
+        <v>153</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1021,11 +1021,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>747</v>
+        <v>332</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1036,11 +1036,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>59</v>
+        <v>644</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1051,11 +1051,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>458</v>
+        <v>896</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1066,11 +1066,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>439</v>
+        <v>984</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1081,11 +1081,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>915</v>
+        <v>506</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1096,11 +1096,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>514</v>
+        <v>209</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>369</v>
+        <v>996</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>394</v>
+        <v>527</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1141,11 +1141,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>858</v>
+        <v>516</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1156,11 +1156,11 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>817</v>
+        <v>711</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1171,11 +1171,11 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>676</v>
+        <v>435</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1186,11 +1186,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>28415-08400</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>240</v>
+        <v>870</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1201,11 +1201,11 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>472</v>
+        <v>510</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1216,11 +1216,11 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>828</v>
+        <v>94</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1231,11 +1231,11 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>311</v>
+        <v>41</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1246,11 +1246,11 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>336</v>
+        <v>309</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -1261,11 +1261,11 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>984</v>
+        <v>291</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1276,11 +1276,11 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>85</v>
+        <v>560</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1291,11 +1291,11 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1306,11 +1306,11 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>174</v>
+        <v>589</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>86</v>
+        <v>801</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1336,11 +1336,11 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>974</v>
+        <v>572</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1351,11 +1351,11 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>356</v>
+        <v>125</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>638</v>
+        <v>126</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -1381,11 +1381,11 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>731</v>
+        <v>803</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -1396,11 +1396,11 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>451</v>
+        <v>853</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -1411,11 +1411,11 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>28415-08400</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>178</v>
+        <v>565</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -1426,11 +1426,11 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>921</v>
+        <v>788</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -1441,11 +1441,11 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>170</v>
+        <v>461</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -1456,11 +1456,11 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>113</v>
+        <v>233</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -1471,11 +1471,11 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>220</v>
+        <v>114</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -1486,11 +1486,11 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>429</v>
+        <v>859</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -1501,11 +1501,11 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>577</v>
+        <v>779</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -1516,11 +1516,11 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>957</v>
+        <v>314</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -1531,11 +1531,11 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>563</v>
+        <v>470</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>686</v>
+        <v>366</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -1561,11 +1561,11 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>314</v>
+        <v>459</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -1576,11 +1576,11 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>108</v>
+        <v>804</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -1591,11 +1591,11 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>412</v>
+        <v>224</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -1606,11 +1606,11 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>572</v>
+        <v>612</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -1621,11 +1621,11 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>167</v>
+        <v>369</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -1636,11 +1636,11 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>379</v>
+        <v>634</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -1651,11 +1651,11 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -1666,11 +1666,11 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>311</v>
+        <v>640</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -1681,11 +1681,11 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>28415-08400</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>650</v>
+        <v>813</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -1696,11 +1696,11 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>501</v>
+        <v>843</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>109</v>
+        <v>834</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>221</v>
+        <v>593</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -1741,11 +1741,11 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>663</v>
+        <v>555</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>93</v>
+        <v>621</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -1771,11 +1771,11 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>874</v>
+        <v>182</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -1786,11 +1786,11 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>325</v>
+        <v>730</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -1801,11 +1801,11 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>492</v>
+        <v>306</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -1816,11 +1816,11 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>926</v>
+        <v>283</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -1831,11 +1831,11 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>28415-08400</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>281</v>
+        <v>931</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -1846,11 +1846,11 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>667</v>
+        <v>844</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -1861,11 +1861,11 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>406</v>
+        <v>148</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -1876,11 +1876,11 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>389</v>
+        <v>950</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -1891,11 +1891,11 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>388</v>
+        <v>293</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -1906,11 +1906,11 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>466</v>
+        <v>139</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -1921,11 +1921,11 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>279</v>
+        <v>896</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -1936,11 +1936,11 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>486</v>
+        <v>265</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -1951,11 +1951,11 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>241</v>
+        <v>738</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -1966,11 +1966,11 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>587</v>
+        <v>858</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -1981,11 +1981,11 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>164</v>
+        <v>789</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -1996,11 +1996,11 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>693</v>
+        <v>412</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -2011,11 +2011,11 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>97</v>
+        <v>155</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -2026,11 +2026,11 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>28415-08400</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>362</v>
+        <v>657</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -2041,11 +2041,11 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>433</v>
+        <v>652</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -2056,11 +2056,11 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>242</v>
+        <v>394</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -2071,11 +2071,11 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -2086,11 +2086,11 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>848</v>
+        <v>823</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -2101,11 +2101,11 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>438</v>
+        <v>422</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>713</v>
+        <v>777</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -2131,11 +2131,11 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>596</v>
+        <v>721</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -2146,11 +2146,11 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>497</v>
+        <v>475</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -2161,11 +2161,11 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>90</v>
+        <v>345</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -2176,11 +2176,11 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>934</v>
+        <v>12</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>45</v>
+        <v>105</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -2206,11 +2206,11 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>594</v>
+        <v>479</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -2221,11 +2221,11 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>829</v>
+        <v>690</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -2236,11 +2236,11 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>703</v>
+        <v>376</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -2251,11 +2251,11 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>160</v>
+        <v>824</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -2266,11 +2266,11 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>982</v>
+        <v>417</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -2281,11 +2281,11 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>187</v>
+        <v>449</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -2296,11 +2296,11 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>226</v>
+        <v>516</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -2311,11 +2311,11 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>139</v>
+        <v>340</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -2326,11 +2326,11 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>443</v>
+        <v>355</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -2341,11 +2341,11 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>709</v>
+        <v>601</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -2356,11 +2356,11 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>216</v>
+        <v>589</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -2371,11 +2371,11 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>28415-08400</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>161</v>
+        <v>817</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -2386,11 +2386,11 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>274</v>
+        <v>925</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -2401,11 +2401,11 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>942</v>
+        <v>790</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -2416,11 +2416,11 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>946</v>
+        <v>57</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>99</v>
+        <v>651</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -2446,11 +2446,11 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>579</v>
+        <v>26</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -2461,11 +2461,11 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>575</v>
+        <v>961</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -2476,11 +2476,11 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>887</v>
+        <v>461</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -2491,11 +2491,11 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>542</v>
+        <v>10</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -2506,11 +2506,11 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>949</v>
+        <v>217</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -2521,11 +2521,11 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>815</v>
+        <v>941</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -2536,11 +2536,11 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>648</v>
+        <v>913</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -2551,11 +2551,11 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>545</v>
+        <v>319</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -2566,11 +2566,11 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>125</v>
+        <v>905</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -2581,11 +2581,11 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>163</v>
+        <v>105</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -2596,11 +2596,11 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>590</v>
+        <v>379</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -2611,11 +2611,11 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>606</v>
+        <v>94</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -2626,11 +2626,11 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>957</v>
+        <v>690</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -2641,11 +2641,11 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>586</v>
+        <v>179</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -2656,11 +2656,11 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>814</v>
+        <v>415</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -2671,11 +2671,11 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>898</v>
+        <v>322</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -2686,11 +2686,11 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>911</v>
+        <v>726</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -2701,11 +2701,11 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>908</v>
+        <v>449</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -2716,11 +2716,11 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>280</v>
+        <v>103</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -2731,11 +2731,11 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>680</v>
+        <v>107</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -2746,11 +2746,11 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>595</v>
+        <v>228</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -2761,11 +2761,11 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>494</v>
+        <v>89</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -2776,11 +2776,11 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>186</v>
+        <v>617</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -2791,11 +2791,11 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>422</v>
+        <v>541</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -2806,630 +2806,15 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>643</v>
+        <v>465</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
           <t>2026-02-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>A6722031002</t>
-        </is>
-      </c>
-      <c r="B161" t="n">
-        <v>707</v>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>28674-L5500</t>
-        </is>
-      </c>
-      <c r="B162" t="n">
-        <v>421</v>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>29673-2F900</t>
-        </is>
-      </c>
-      <c r="B163" t="n">
-        <v>415</v>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>28422-2M100</t>
-        </is>
-      </c>
-      <c r="B164" t="n">
-        <v>717</v>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>29696-2U000</t>
-        </is>
-      </c>
-      <c r="B165" t="n">
-        <v>60</v>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>28674-L5500</t>
-        </is>
-      </c>
-      <c r="B166" t="n">
-        <v>496</v>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>28421-2M100</t>
-        </is>
-      </c>
-      <c r="B167" t="n">
-        <v>928</v>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>28422-2M100</t>
-        </is>
-      </c>
-      <c r="B168" t="n">
-        <v>30</v>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>28422-2M100</t>
-        </is>
-      </c>
-      <c r="B169" t="n">
-        <v>847</v>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>28421-2M100</t>
-        </is>
-      </c>
-      <c r="B170" t="n">
-        <v>328</v>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>28421-2M100</t>
-        </is>
-      </c>
-      <c r="B171" t="n">
-        <v>873</v>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>25451-P7200</t>
-        </is>
-      </c>
-      <c r="B172" t="n">
-        <v>888</v>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>28674-L5500</t>
-        </is>
-      </c>
-      <c r="B173" t="n">
-        <v>711</v>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>29673-2F910</t>
-        </is>
-      </c>
-      <c r="B174" t="n">
-        <v>899</v>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>29696-2U000</t>
-        </is>
-      </c>
-      <c r="B175" t="n">
-        <v>147</v>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>2026-02-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>28421-2M100</t>
-        </is>
-      </c>
-      <c r="B176" t="n">
-        <v>771</v>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>25451-P7200</t>
-        </is>
-      </c>
-      <c r="B177" t="n">
-        <v>802</v>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>28422-2M100</t>
-        </is>
-      </c>
-      <c r="B178" t="n">
-        <v>285</v>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>28674-L5500</t>
-        </is>
-      </c>
-      <c r="B179" t="n">
-        <v>436</v>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>A6722031002</t>
-        </is>
-      </c>
-      <c r="B180" t="n">
-        <v>671</v>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>29673-2F910</t>
-        </is>
-      </c>
-      <c r="B181" t="n">
-        <v>202</v>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>2026-02-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>25451-P7200</t>
-        </is>
-      </c>
-      <c r="B182" t="n">
-        <v>226</v>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>2026-02-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>25450-P7200</t>
-        </is>
-      </c>
-      <c r="B183" t="n">
-        <v>768</v>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>2026-02-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>25451-P7200</t>
-        </is>
-      </c>
-      <c r="B184" t="n">
-        <v>787</v>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>A6722030900</t>
-        </is>
-      </c>
-      <c r="B185" t="n">
-        <v>898</v>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>2026-02-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>28422-2M100</t>
-        </is>
-      </c>
-      <c r="B186" t="n">
-        <v>850</v>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>29673-2F900</t>
-        </is>
-      </c>
-      <c r="B187" t="n">
-        <v>537</v>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>29673-2R060</t>
-        </is>
-      </c>
-      <c r="B188" t="n">
-        <v>77</v>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>28421-2M100</t>
-        </is>
-      </c>
-      <c r="B189" t="n">
-        <v>736</v>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>A6722030900</t>
-        </is>
-      </c>
-      <c r="B190" t="n">
-        <v>423</v>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>29673-2R060</t>
-        </is>
-      </c>
-      <c r="B191" t="n">
-        <v>809</v>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>A6722030900</t>
-        </is>
-      </c>
-      <c r="B192" t="n">
-        <v>910</v>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>A6722031002</t>
-        </is>
-      </c>
-      <c r="B193" t="n">
-        <v>39</v>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>29673-2R060</t>
-        </is>
-      </c>
-      <c r="B194" t="n">
-        <v>207</v>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>29696-2U000</t>
-        </is>
-      </c>
-      <c r="B195" t="n">
-        <v>867</v>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>29673-2F900</t>
-        </is>
-      </c>
-      <c r="B196" t="n">
-        <v>265</v>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>29673-2F900</t>
-        </is>
-      </c>
-      <c r="B197" t="n">
-        <v>477</v>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>29673-2F900</t>
-        </is>
-      </c>
-      <c r="B198" t="n">
-        <v>950</v>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>28422-2M100</t>
-        </is>
-      </c>
-      <c r="B199" t="n">
-        <v>731</v>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>29696-2U000</t>
-        </is>
-      </c>
-      <c r="B200" t="n">
-        <v>290</v>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>28422-2M100</t>
-        </is>
-      </c>
-      <c r="B201" t="n">
-        <v>853</v>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
         </is>
       </c>
     </row>
